--- a/Lab5/Lab5.xlsx
+++ b/Lab5/Lab5.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="242">
   <si>
     <t>TEST CASE ID:</t>
   </si>
@@ -155,6 +155,24 @@
     <t>Trả về 5</t>
   </si>
   <si>
+    <t>Trả về 100</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Gọi factorial(1)</t>
+  </si>
+  <si>
+    <t>Trả về 2</t>
+  </si>
+  <si>
+    <t>Trả về 6</t>
+  </si>
+  <si>
+    <t>Gọi plus(2,-3)</t>
+  </si>
+  <si>
     <t>TC_SUITE_01</t>
   </si>
   <si>
@@ -200,6 +218,39 @@
     <t>In chuỗi SuiteTest2</t>
   </si>
   <si>
+    <t>In chuỗi "Running SuiteTest2"</t>
+  </si>
+  <si>
+    <t>Running SuiteTest1</t>
+  </si>
+  <si>
+    <t>Không in gì ra console</t>
+  </si>
+  <si>
+    <t>Running SuiteTest2</t>
+  </si>
+  <si>
+    <t>Chạy Test Suite khi thiếu SuiteTest2</t>
+  </si>
+  <si>
+    <t>Throw ClassNotFoundException</t>
+  </si>
+  <si>
+    <t>Chạy Test Suite khi JUnit chưa cấu hình</t>
+  </si>
+  <si>
+    <t>Test Suite không chạy</t>
+  </si>
+  <si>
+    <t>Compile Error</t>
+  </si>
+  <si>
+    <t>Chạy Suite Runner với tên class sai</t>
+  </si>
+  <si>
+    <t>Không in gì</t>
+  </si>
+  <si>
     <t>TC_ANNOTATION_01</t>
   </si>
   <si>
@@ -251,6 +302,33 @@
     <t>Chạy @AfterClass</t>
   </si>
   <si>
+    <t>Chạy @Before khi method không static</t>
+  </si>
+  <si>
+    <t>Không chạy</t>
+  </si>
+  <si>
+    <t>Chạy @After khi method bị comment</t>
+  </si>
+  <si>
+    <t>Chạy @Test có annotation @Ignore</t>
+  </si>
+  <si>
+    <t>Không chạy test</t>
+  </si>
+  <si>
+    <t>Test vẫn chạy</t>
+  </si>
+  <si>
+    <t>Chạy test class thiếu @AfterClass</t>
+  </si>
+  <si>
+    <t>In thông báo AfterClass</t>
+  </si>
+  <si>
+    <t>Chạy @BeforeClass khai báo sai cú pháp</t>
+  </si>
+  <si>
     <t>Kiểm thử tính tiền theo tuổi</t>
   </si>
   <si>
@@ -311,6 +389,21 @@
     <t>Báo lỗi</t>
   </si>
   <si>
+    <t>Nhập tuổi = "abc"</t>
+  </si>
+  <si>
+    <t>Không xử lý</t>
+  </si>
+  <si>
+    <t>Nhập tuổi = 10.5</t>
+  </si>
+  <si>
+    <t>Làm tròn / vẫn tính</t>
+  </si>
+  <si>
+    <t>Không nhập tuổi</t>
+  </si>
+  <si>
     <t>TC_REGISTER_FORM</t>
   </si>
   <si>
@@ -381,9 +474,6 @@
   </si>
   <si>
     <t>Hiển thị lỗi</t>
-  </si>
-  <si>
-    <t>Fail</t>
   </si>
   <si>
     <t>Nhập Mã KH &lt; 6 ký tự</t>
@@ -1337,7 +1427,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1371,24 +1461,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1398,53 +1485,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1979,247 +2084,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.8181818181818" style="15" customWidth="1"/>
-    <col min="2" max="2" width="22.4545454545455" style="15" customWidth="1"/>
-    <col min="3" max="3" width="21.2727272727273" style="15" customWidth="1"/>
-    <col min="4" max="4" width="22.4545454545455" style="15" customWidth="1"/>
-    <col min="5" max="5" width="58.7272727272727" style="15" customWidth="1"/>
-    <col min="6" max="6" width="8.45454545454546" style="15" customWidth="1"/>
-    <col min="7" max="7" width="4.09090909090909" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="15"/>
+    <col min="1" max="1" width="14.8181818181818" style="36" customWidth="1"/>
+    <col min="2" max="2" width="22.4545454545455" style="36" customWidth="1"/>
+    <col min="3" max="3" width="21.2727272727273" style="36" customWidth="1"/>
+    <col min="4" max="4" width="22.4545454545455" style="36" customWidth="1"/>
+    <col min="5" max="5" width="58.7272727272727" style="36" customWidth="1"/>
+    <col min="6" max="6" width="8.45454545454546" style="36" customWidth="1"/>
+    <col min="7" max="7" width="4.09090909090909" style="36" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="18"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="18" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="19">
         <v>46049</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="39" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="25">
+      <c r="A9" s="40">
         <v>1</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="40">
         <v>1</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="39" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="A10" s="40">
         <v>2</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="40">
         <v>2</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="39" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" ht="29" spans="1:5">
-      <c r="A11" s="25">
+      <c r="A11" s="40">
         <v>3</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="40">
         <v>3</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="39" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" ht="29" spans="1:5">
-      <c r="A12" s="25">
+      <c r="A12" s="40">
         <v>4</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="40">
         <v>4</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="39" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="17" t="s">
         <v>24</v>
       </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25">
+      <c r="A16" s="40">
         <v>1</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="40">
         <v>120</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="25">
+      <c r="A17" s="40">
         <v>2</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="40">
         <v>1</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" ht="43.5" spans="1:5">
-      <c r="A18" s="25">
+      <c r="A18" s="40">
         <v>3</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="25">
+      <c r="A19" s="40">
         <v>4</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="40">
         <v>5</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="39" t="s">
         <v>32</v>
       </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
+        <v>5</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="25">
+        <v>120</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="25">
+        <v>6</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
+        <v>7</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="25">
+        <v>1</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="25">
+        <v>8</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="25">
+        <v>5</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="43.5" spans="1:5">
+      <c r="A24" s="25">
+        <v>9</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="25">
+        <v>-1</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2230,7 +2442,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.9090909090909" style="15" customWidth="1"/>
@@ -2248,194 +2460,278 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+        <v>47</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="19">
         <v>46049</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" ht="29" spans="1:5">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="29" spans="1:5">
-      <c r="A9" s="25">
+      <c r="A9" s="22">
         <v>1</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="25">
+      <c r="B9" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="22">
         <v>1</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>43</v>
+      <c r="E9" s="22" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="29" spans="1:5">
-      <c r="A10" s="25">
+      <c r="A10" s="22">
         <v>2</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="B10" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="22">
         <v>2</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>45</v>
+      <c r="E10" s="22" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="29" spans="1:5">
-      <c r="A11" s="25">
+      <c r="A11" s="22">
         <v>3</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="25">
+      <c r="B11" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="22">
         <v>3</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>47</v>
+      <c r="E11" s="22" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="29" spans="1:5">
-      <c r="A12" s="25">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="25">
+      <c r="B12" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="22">
         <v>4</v>
       </c>
-      <c r="E12" s="25" t="s">
-        <v>49</v>
+      <c r="E12" s="22" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25">
+      <c r="A16" s="22">
         <v>1</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="25" t="s">
+      <c r="B16" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="25">
+      <c r="A17" s="22">
         <v>2</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="25" t="s">
+      <c r="B17" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="18" ht="29" spans="1:5">
+      <c r="A18" s="23">
+        <v>3</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="23">
+        <v>4</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" ht="29" spans="1:5">
+      <c r="A20" s="23">
+        <v>5</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" ht="29" spans="1:5">
+      <c r="A21" s="23">
+        <v>6</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" ht="29" spans="1:5">
+      <c r="A22" s="23">
+        <v>7</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2447,7 +2743,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.9090909090909" style="26" customWidth="1"/>
@@ -2464,245 +2760,329 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+        <v>73</v>
+      </c>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="29"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="31">
         <v>46049</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="30" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" ht="29" spans="1:5">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="32" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="29" spans="1:5">
-      <c r="A9" s="35">
+      <c r="A9" s="33">
         <v>1</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="35">
+      <c r="B9" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="33">
         <v>1</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" ht="29" spans="1:5">
+      <c r="A10" s="33">
+        <v>2</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="33">
+        <v>2</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" ht="29" spans="1:5">
+      <c r="A11" s="33">
+        <v>3</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="33">
+        <v>3</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" ht="29" spans="1:5">
+      <c r="A12" s="33">
+        <v>4</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="33">
+        <v>4</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="33">
+        <v>1</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="33" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" ht="29" spans="1:5">
-      <c r="A10" s="35">
+      <c r="E16" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="33">
         <v>2</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="35">
-        <v>2</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" ht="29" spans="1:5">
-      <c r="A11" s="35">
+      <c r="B17" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="33">
         <v>3</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="35">
-        <v>3</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" ht="29" spans="1:5">
-      <c r="A12" s="35">
+      <c r="B18" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="33">
         <v>4</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="35">
-        <v>4</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="35">
-        <v>1</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="35" t="s">
+      <c r="B19" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="35">
-        <v>2</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="35" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="33">
+        <v>5</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="35">
-        <v>3</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="35" t="s">
+    <row r="21" ht="29" spans="1:5">
+      <c r="A21" s="34">
+        <v>6</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" ht="29" spans="1:5">
+      <c r="A22" s="34">
+        <v>7</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" ht="29" spans="1:5">
+      <c r="A23" s="34">
+        <v>8</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="29" spans="1:5">
+      <c r="A24" s="34">
+        <v>9</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" ht="29" spans="1:5">
+      <c r="A25" s="34">
+        <v>10</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="35">
-        <v>4</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="35">
-        <v>5</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>32</v>
+      <c r="E25" s="35" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2714,7 +3094,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.9090909090909" style="15" customWidth="1"/>
@@ -2730,245 +3110,363 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+        <v>98</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="19">
         <v>46049</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" ht="29" spans="1:5">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>73</v>
+      <c r="E8" s="21" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="25">
+      <c r="A9" s="22">
         <v>1</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="25">
+      <c r="B9" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="22">
         <v>1</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>75</v>
+      <c r="E9" s="22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="A10" s="22">
         <v>2</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="B10" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="22">
         <v>2</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>77</v>
+      <c r="E10" s="22" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="25">
+      <c r="A11" s="22">
         <v>3</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="25">
+      <c r="B11" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="22">
         <v>3</v>
       </c>
-      <c r="E11" s="25" t="s">
-        <v>79</v>
+      <c r="E11" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="25">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="25">
+      <c r="B12" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="22">
         <v>4</v>
       </c>
-      <c r="E12" s="25" t="s">
-        <v>81</v>
+      <c r="E12" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25">
+      <c r="A16" s="22">
         <v>1</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="25">
+      <c r="B16" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="22">
         <v>0</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="25">
+      <c r="A17" s="22">
         <v>2</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="25">
+      <c r="B17" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="22">
         <v>50000</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="25">
+      <c r="A18" s="22">
         <v>3</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="25">
+      <c r="B18" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="22">
         <v>100000</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="25">
+      <c r="A19" s="22">
         <v>4</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="25">
+      <c r="B19" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="22">
         <v>70000</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="A20" s="22">
         <v>5</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="25" t="s">
+      <c r="B20" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="22" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="23">
+        <v>6</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="25">
+        <v>0</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="23">
+        <v>7</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="25">
+        <v>50000</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="23">
+        <v>8</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="25">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="23">
+        <v>9</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="25">
+        <v>70000</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="23">
+        <v>10</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="23">
+        <v>11</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="23">
+        <v>12</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2983,7 +3481,9 @@
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="36.6363636363636" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="16384" width="36.6363636363636" customWidth="1"/>
+    <col min="1" max="3" width="36.6363636363636" style="13" customWidth="1"/>
+    <col min="4" max="4" width="53.5454545454545" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="36.6363636363636" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2991,50 +3491,50 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="D1" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="15"/>
@@ -3054,677 +3554,677 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="19">
         <v>46049</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
-    <row r="8" ht="43.5" spans="1:5">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="29" spans="1:5">
-      <c r="A9" s="3">
+    <row r="9" spans="1:5">
+      <c r="A9" s="10">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="B9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="10">
         <v>1</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" ht="43.5" spans="1:5">
-      <c r="A10" s="3">
+      <c r="E9" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="B10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="10">
         <v>2</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" ht="58" spans="1:5">
-      <c r="A11" s="3">
+      <c r="E10" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="10">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="B11" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="10">
         <v>3</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" ht="43.5" spans="1:5">
-      <c r="A12" s="3">
+      <c r="E11" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10">
         <v>4</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B12" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="10">
         <v>4</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" ht="29" spans="1:5">
-      <c r="A13" s="3">
+      <c r="E12" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="10">
         <v>5</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="B13" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="10">
         <v>5</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" ht="43.5" spans="4:5">
-      <c r="D14" s="3">
+      <c r="E13" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5">
+      <c r="D14" s="10">
         <v>6</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" ht="58" spans="4:5">
-      <c r="D15" s="3">
+      <c r="E14" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="4:5">
+      <c r="D15" s="10">
         <v>7</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" ht="43.5" spans="4:5">
-      <c r="D16" s="3">
+      <c r="E15" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5">
+      <c r="D16" s="10">
         <v>8</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" ht="29" spans="4:5">
-      <c r="D17" s="3">
+      <c r="E16" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
+      <c r="D17" s="10">
         <v>9</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" ht="43.5" spans="4:5">
-      <c r="D18" s="3">
+      <c r="E17" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
+      <c r="D18" s="10">
         <v>10</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>108</v>
+      <c r="E18" s="10" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" ht="43.5" spans="1:5">
-      <c r="A23" s="3">
+      <c r="E22" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" ht="29" spans="1:5">
+      <c r="A23" s="10">
         <v>1</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="B23" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" ht="29" spans="1:5">
-      <c r="A24" s="3">
+    <row r="24" spans="1:5">
+      <c r="A24" s="10">
         <v>2</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>116</v>
+      <c r="B24" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3">
+      <c r="A25" s="10">
         <v>3</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>116</v>
+      <c r="B25" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3">
+      <c r="A26" s="10">
         <v>4</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" ht="29" spans="1:5">
-      <c r="A27" s="3">
+      <c r="B26" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="10">
         <v>5</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28" ht="29" spans="1:5">
-      <c r="A28" s="3">
+      <c r="B27" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="10">
         <v>6</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>116</v>
+      <c r="B28" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3">
+      <c r="A29" s="10">
         <v>7</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>116</v>
+      <c r="B29" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3">
+      <c r="A30" s="10">
         <v>8</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>116</v>
+      <c r="B30" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3">
+      <c r="A31" s="10">
         <v>9</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>116</v>
+      <c r="B31" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3">
+      <c r="A32" s="10">
         <v>10</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" ht="29" spans="1:5">
-      <c r="A33" s="3">
+      <c r="B32" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="10">
         <v>11</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>116</v>
+      <c r="B33" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3">
+      <c r="A34" s="10">
         <v>12</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>116</v>
+      <c r="B34" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3">
+      <c r="A35" s="10">
         <v>13</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>116</v>
+      <c r="B35" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3">
+      <c r="A36" s="10">
         <v>14</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" ht="29" spans="1:5">
-      <c r="A37" s="3">
+      <c r="B36" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="10">
         <v>15</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>116</v>
+      <c r="B37" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3">
+      <c r="A38" s="10">
         <v>16</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>116</v>
+      <c r="B38" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3">
+      <c r="A39" s="10">
         <v>17</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>116</v>
+      <c r="B39" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3">
+      <c r="A40" s="10">
         <v>18</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>116</v>
+      <c r="B40" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="3">
+      <c r="A41" s="10">
         <v>19</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>116</v>
+      <c r="B41" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="3">
+      <c r="A42" s="10">
         <v>20</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>116</v>
+      <c r="B42" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="3">
+      <c r="A43" s="10">
         <v>21</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" ht="29" spans="1:5">
-      <c r="A44" s="3">
+      <c r="B43" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="10">
         <v>22</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" ht="29" spans="1:5">
-      <c r="A45" s="3">
+      <c r="B44" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="10">
         <v>23</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>116</v>
+      <c r="B45" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="3">
+      <c r="A46" s="10">
         <v>24</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="47" ht="29" spans="1:5">
-      <c r="A47" s="3">
+      <c r="E46" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="10">
         <v>25</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>116</v>
+      <c r="B47" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="3">
+      <c r="A48" s="10">
         <v>26</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="B48" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="10">
+        <v>27</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="10">
+        <v>28</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" ht="29" spans="1:5">
-      <c r="A49" s="3">
-        <v>27</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" ht="29" spans="1:5">
-      <c r="A50" s="3">
-        <v>28</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" ht="29" spans="1:5">
-      <c r="A51" s="3">
+      <c r="D50" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="10">
         <v>29</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>116</v>
+      <c r="B51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="3">
+      <c r="A52" s="10">
         <v>30</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="B52" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3753,18 +4253,18 @@
   <sheetData>
     <row r="1" spans="3:3">
       <c r="C1" s="5" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>5</v>
@@ -3772,13 +4272,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
@@ -3786,21 +4286,21 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="6" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="4" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E5" s="8">
         <v>46049</v>
@@ -3808,7 +4308,7 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C6" s="7">
         <v>0.1</v>
@@ -3816,34 +4316,34 @@
     </row>
     <row r="8" ht="29" spans="1:10">
       <c r="A8" s="9" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3851,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C9" s="10">
         <v>24</v>
@@ -3874,7 +4374,7 @@
       <c r="I9" s="10">
         <v>24</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3883,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>
@@ -3906,7 +4406,7 @@
       <c r="I10" s="10">
         <v>3</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3915,7 +4415,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -3938,14 +4438,14 @@
       <c r="I11" s="10">
         <v>3</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
-        <v>180</v>
+      <c r="B12" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="C12" s="9">
         <v>30</v>
@@ -3968,7 +4468,7 @@
       <c r="I12" s="9">
         <v>30</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <v>1</v>
       </c>
     </row>
@@ -4002,55 +4502,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -4058,7 +4558,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -4066,7 +4566,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="B9" s="2">
         <v>46049</v>
@@ -4074,58 +4574,58 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" ht="72.5" spans="1:2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" ht="43.5" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
